--- a/data/trans_camb/IP12-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 11,14</t>
+          <t>-1,51; 11,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 13,53</t>
+          <t>-2,54; 13,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 7,62</t>
+          <t>-6,79; 7,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 8,54</t>
+          <t>-4,81; 8,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 3,05</t>
+          <t>-8,58; 2,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 13,38</t>
+          <t>-2,1; 13,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 8,06</t>
+          <t>-1,31; 8,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 5,88</t>
+          <t>-3,56; 5,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 8,73</t>
+          <t>-2,78; 8,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 354,34</t>
+          <t>-22,76; 357,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 374,57</t>
+          <t>-37,37; 392,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 226,92</t>
+          <t>-73,7; 202,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 270,76</t>
+          <t>-54,15; 227,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 126,73</t>
+          <t>-100,0; 132,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 390,71</t>
+          <t>-32,38; 421,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 200,04</t>
+          <t>-17,18; 203,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 146,58</t>
+          <t>-44,11; 155,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 199,5</t>
+          <t>-37,6; 182,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,63</t>
+          <t>-2,24; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,51</t>
+          <t>-2,75; 2,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,78</t>
+          <t>-2,85; 2,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,3</t>
+          <t>-0,25; 5,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,31</t>
+          <t>-2,17; 3,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,66</t>
+          <t>-1,99; 3,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,81</t>
+          <t>-0,42; 3,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,2</t>
+          <t>-1,63; 2,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,29</t>
+          <t>-1,67; 2,27</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 68,17</t>
+          <t>-26,07; 56,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 46,52</t>
+          <t>-33,59; 43,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 50,63</t>
+          <t>-35,6; 48,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 102,01</t>
+          <t>-5,37; 97,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 60,04</t>
+          <t>-27,29; 56,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 68,27</t>
+          <t>-25,41; 64,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 66,46</t>
+          <t>-6,0; 65,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 37,87</t>
+          <t>-20,73; 36,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 38,71</t>
+          <t>-21,35; 39,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 10,07</t>
+          <t>0,27; 9,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,11</t>
+          <t>0,58; 9,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,49</t>
+          <t>-1,05; 7,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,88</t>
+          <t>-4,16; 5,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,74</t>
+          <t>-5,26; 2,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,09</t>
+          <t>-3,27; 5,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,7</t>
+          <t>-0,61; 5,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,99</t>
+          <t>-1,25; 4,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,48</t>
+          <t>-1,34; 5,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 310,04</t>
+          <t>1,8; 302,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 277,11</t>
+          <t>0,4; 286,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 225,04</t>
+          <t>-19,81; 219,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,6; 120,99</t>
+          <t>-51,11; 139,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 72,42</t>
+          <t>-63,15; 68,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 147,07</t>
+          <t>-38,88; 140,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 131,93</t>
+          <t>-10,35; 138,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 118,84</t>
+          <t>-17,41; 119,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 126,29</t>
+          <t>-20,28; 125,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,46</t>
+          <t>-0,31; 4,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,77</t>
+          <t>-0,9; 3,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,15</t>
+          <t>-1,6; 3,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,14</t>
+          <t>-0,46; 4,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,9</t>
+          <t>-2,25; 1,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,45</t>
+          <t>-1,11; 3,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,74</t>
+          <t>0,35; 3,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,19</t>
+          <t>-0,72; 2,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,5</t>
+          <t>-0,62; 2,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 80,85</t>
+          <t>-5,0; 81,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 69,18</t>
+          <t>-13,17; 66,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 59,72</t>
+          <t>-21,81; 55,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 73,68</t>
+          <t>-6,54; 75,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 33,74</t>
+          <t>-29,5; 33,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 62,55</t>
+          <t>-15,74; 64,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 64,64</t>
+          <t>4,41; 66,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 37,02</t>
+          <t>-10,61; 41,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 43,51</t>
+          <t>-9,24; 44,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 11,99</t>
+          <t>-1,64; 11,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 13,25</t>
+          <t>-2,24; 14,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,22</t>
+          <t>-5,69; 8,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 8,17</t>
+          <t>-4,25; 8,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 2,62</t>
+          <t>-8,5; 2,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 13,75</t>
+          <t>-1,9; 15,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 8,16</t>
+          <t>-1,25; 8,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,85</t>
+          <t>-4,11; 5,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 8,45</t>
+          <t>-2,68; 8,25</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 357,43</t>
+          <t>-28,61; 308,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 392,07</t>
+          <t>-31,6; 459,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,7; 202,12</t>
+          <t>-67,6; 250,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 227,13</t>
+          <t>-48,13; 279,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 132,83</t>
+          <t>-89,95; 124,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 421,53</t>
+          <t>-31,19; 413,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 203,75</t>
+          <t>-20,39; 188,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 155,1</t>
+          <t>-47,57; 123,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 182,86</t>
+          <t>-35,61; 196,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,33</t>
+          <t>-2,33; 3,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,45</t>
+          <t>-2,96; 2,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,71</t>
+          <t>-2,89; 2,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,34</t>
+          <t>-0,29; 5,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,16</t>
+          <t>-2,05; 3,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,54</t>
+          <t>-1,81; 3,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,83</t>
+          <t>-0,26; 3,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,27</t>
+          <t>-1,55; 2,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,27</t>
+          <t>-1,75; 2,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 56,36</t>
+          <t>-27,58; 64,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 43,38</t>
+          <t>-33,9; 48,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 48,19</t>
+          <t>-34,06; 47,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 97,9</t>
+          <t>-4,39; 93,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 56,78</t>
+          <t>-24,63; 61,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 64,56</t>
+          <t>-23,48; 62,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 65,5</t>
+          <t>-4,59; 61,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 36,89</t>
+          <t>-20,15; 35,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 39,43</t>
+          <t>-22,2; 36,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 9,42</t>
+          <t>0,55; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 9,41</t>
+          <t>0,61; 9,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,4</t>
+          <t>-0,64; 8,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,49</t>
+          <t>-4,29; 4,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,67</t>
+          <t>-5,23; 3,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,84</t>
+          <t>-3,72; 5,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,7</t>
+          <t>-0,95; 5,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,9</t>
+          <t>-1,35; 4,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,23</t>
+          <t>-1,05; 5,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 302,68</t>
+          <t>5,79; 293,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 286,13</t>
+          <t>6,58; 297,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 219,23</t>
+          <t>-14,93; 251,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 139,97</t>
+          <t>-54,99; 118,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,15; 68,4</t>
+          <t>-60,48; 84,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 140,32</t>
+          <t>-45,98; 128,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 138,93</t>
+          <t>-13,98; 131,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 119,49</t>
+          <t>-20,44; 113,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 125,63</t>
+          <t>-17,5; 125,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,41</t>
+          <t>-0,17; 4,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,59</t>
+          <t>-0,62; 3,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,07</t>
+          <t>-1,77; 2,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,07</t>
+          <t>-0,39; 3,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,93</t>
+          <t>-2,03; 2,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,6</t>
+          <t>-1,01; 3,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,78</t>
+          <t>0,42; 3,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,37</t>
+          <t>-0,87; 2,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,57</t>
+          <t>-0,74; 2,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 81,05</t>
+          <t>-2,67; 84,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 66,76</t>
+          <t>-10,06; 71,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 55,67</t>
+          <t>-23,89; 49,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 75,09</t>
+          <t>-5,7; 71,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 33,94</t>
+          <t>-27,48; 36,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 64,01</t>
+          <t>-13,6; 69,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 66,7</t>
+          <t>5,85; 62,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 41,08</t>
+          <t>-11,65; 36,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 44,53</t>
+          <t>-10,93; 45,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,07</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,86</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>3,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 11,65</t>
+          <t>-4,95; 8,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 14,36</t>
+          <t>-8,27; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 8,64</t>
+          <t>-2,3; 14,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 8,55</t>
+          <t>-2,15; 11,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 2,45</t>
+          <t>-1,95; 13,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 15,07</t>
+          <t>-5,25; 8,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 8,07</t>
+          <t>-1,43; 8,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 5,71</t>
+          <t>-3,66; 5,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 8,25</t>
+          <t>-1,8; 10,12</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-48,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>75,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>78,13%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-48,51%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 308,34</t>
+          <t>-53,52; 270,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 459,24</t>
+          <t>-100,0; 126,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 250,91</t>
+          <t>-40,51; 415,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 279,36</t>
+          <t>-28,84; 354,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,95; 124,07</t>
+          <t>-30,88; 374,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 413,78</t>
+          <t>-69,24; 285,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 188,36</t>
+          <t>-18,95; 200,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 123,73</t>
+          <t>-46,68; 146,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 196,97</t>
+          <t>-26,5; 223,95</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,92</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,55</t>
+          <t>-0,25; 5,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,69</t>
+          <t>-1,83; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,82</t>
+          <t>-1,85; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,23</t>
+          <t>-2,22; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,35</t>
+          <t>-3,03; 2,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,45</t>
+          <t>-2,85; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,86</t>
+          <t>-0,43; 3,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,1</t>
+          <t>-1,74; 2,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,21</t>
+          <t>-1,56; 2,59</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-3,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,19%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36,41%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 64,62</t>
+          <t>-3,36; 102,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 48,49</t>
+          <t>-23,63; 60,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 47,18</t>
+          <t>-23,54; 70,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 93,27</t>
+          <t>-26,82; 68,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 61,54</t>
+          <t>-35,02; 46,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 62,64</t>
+          <t>-33,69; 54,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 61,72</t>
+          <t>-6,52; 66,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 35,22</t>
+          <t>-21,54; 37,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 36,72</t>
+          <t>-19,53; 43,61</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>4,75</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>2,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,6</t>
+          <t>-4,07; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 9,43</t>
+          <t>-5,4; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 8,22</t>
+          <t>-3,34; 6,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,63</t>
+          <t>0,63; 10,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,07</t>
+          <t>0,55; 9,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,84</t>
+          <t>-1,15; 7,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,6</t>
+          <t>-1,15; 5,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,63</t>
+          <t>-1,17; 4,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,31</t>
+          <t>-0,96; 5,57</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,5%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18,87%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>96,4%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>96,08%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58,36%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-15,5%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 293,43</t>
+          <t>-51,6; 120,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 297,21</t>
+          <t>-61,24; 72,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 251,65</t>
+          <t>-41,71; 146,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 118,52</t>
+          <t>3,26; 310,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,48; 84,69</t>
+          <t>4,86; 277,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 128,98</t>
+          <t>-21,41; 238,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 131,15</t>
+          <t>-16,61; 131,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 113,76</t>
+          <t>-18,53; 118,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 125,93</t>
+          <t>-16,5; 127,84</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,56</t>
+          <t>-0,36; 4,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,81</t>
+          <t>-2,2; 1,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,7</t>
+          <t>-1,11; 3,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,96</t>
+          <t>-0,06; 4,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,08</t>
+          <t>-0,88; 3,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,79</t>
+          <t>-1,15; 3,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,54</t>
+          <t>0,52; 3,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,13</t>
+          <t>-0,96; 2,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,68</t>
+          <t>-0,57; 2,7</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-0,84%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>33,72%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>22,9%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 84,31</t>
+          <t>-6,34; 73,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 71,9</t>
+          <t>-28,43; 33,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 49,99</t>
+          <t>-15,28; 67,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 71,14</t>
+          <t>-1,3; 80,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 36,95</t>
+          <t>-11,39; 69,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 69,34</t>
+          <t>-15,71; 65,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 62,6</t>
+          <t>6,56; 64,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 36,09</t>
+          <t>-13,03; 37,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 45,88</t>
+          <t>-8,15; 45,92</t>
         </is>
       </c>
     </row>
